--- a/backend/memberfiles/CHUNILAL_BHUT.xlsx
+++ b/backend/memberfiles/CHUNILAL_BHUT.xlsx
@@ -397,18 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="120.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>CHUNILAL</v>
+        <v>Chunilal</v>
       </c>
       <c r="B1" t="str">
-        <v>BHUT</v>
+        <v>Bhut</v>
       </c>
       <c r="C1" t="str">
         <v>csbhut11</v>
@@ -417,7 +413,7 @@
         <v>16016cs@gmail.com</v>
       </c>
       <c r="E1" t="str">
-        <v>LEN-KH3TSY</v>
+        <v>LEN-5824PB</v>
       </c>
     </row>
     <row r="2">
@@ -433,33 +429,9 @@
         <v>Activity</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>4/22/2026</v>
-      </c>
-      <c r="B4" t="str">
-        <v>uploads/1776864663663_CYCLE1 - Copy.png</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>7/13/2026</v>
-      </c>
-      <c r="B5" t="str">
-        <v>pppppppppppppppppp</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>7/13/2026</v>
-      </c>
-      <c r="B6" t="str">
-        <v>uploads/1783963348213_20110519_26.JPG</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>